--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1345,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1372,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1399,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1414,7 +1429,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1426,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1441,7 +1456,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1453,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1468,7 +1483,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1480,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1495,7 +1510,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1507,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1534,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1549,7 +1564,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1561,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1576,7 +1591,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1588,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1615,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1669,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1684,7 +1699,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1696,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1723,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1750,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1777,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1804,83 +1819,110 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>4173905.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>498489.56</t>
+          <t>4318905.1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>495231</t>
+          <t>515751.46</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>495231</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3258.56</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20520.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1252,12 +1252,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1333,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1360,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1414,12 +1414,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1441,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1495,12 +1495,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1522,12 +1522,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1576,12 +1576,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1684,12 +1684,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1846,83 +1846,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>4318905.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>515751.46</t>
+          <t>4318905.1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>495231</t>
+          <t>515751.46</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>512492</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>20520.46</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3259.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1375,7 +1390,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1387,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1414,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1441,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1468,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,7 +1498,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1495,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1510,7 +1525,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1522,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1537,7 +1552,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1549,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1564,7 +1579,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1576,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1603,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1618,7 +1633,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1630,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1645,7 +1660,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1657,12 +1672,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1699,7 +1714,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1711,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1738,12 +1753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1753,7 +1768,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1765,12 +1780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1792,12 +1807,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1819,12 +1834,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1846,12 +1861,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1873,83 +1888,110 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>4318905.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>515751.46</t>
+          <t>4329101.1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>512492</t>
+          <t>516923.41</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>512492</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>3259.46</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4431.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1294,12 +1294,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1375,12 +1375,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1402,12 +1402,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1429,12 +1429,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1456,12 +1456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1510,12 +1510,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1537,12 +1537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1564,12 +1564,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1618,12 +1618,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1726,12 +1726,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1834,12 +1834,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1915,83 +1915,110 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>4329101.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>516923.41</t>
+          <t>4329101.1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>512492</t>
+          <t>516923.41</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>513663</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>4431.41</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3260.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,166 +1167,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1336,7 +1351,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1348,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1375,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1402,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1417,7 +1432,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1429,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1444,7 +1459,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1456,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1483,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1510,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1537,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1552,7 +1567,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1564,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1579,7 +1594,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1591,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1606,7 +1621,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1618,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1633,7 +1648,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1645,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1672,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1687,7 +1702,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1699,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1714,7 +1729,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1768,7 +1783,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1780,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1807,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1822,7 +1837,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1834,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1861,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1888,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1915,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1942,83 +1957,110 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4329101.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>516923.41</t>
+          <t>4339100.1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>513663</t>
+          <t>517875.7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>513663</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>3260.41</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>4212.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1336,12 +1336,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1363,12 +1363,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1390,12 +1390,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1498,12 +1498,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1552,12 +1552,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1606,12 +1606,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1660,12 +1660,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,12 +1930,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1957,12 +1957,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1984,83 +1984,110 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>4339100.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>517875.7</t>
+          <t>4339100.1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>513663</t>
+          <t>517875.7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>514615</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>4212.7</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3260.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,166 +1209,181 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1405,7 +1420,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1417,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1444,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1471,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1486,7 +1501,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1498,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1513,7 +1528,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1525,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1552,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1579,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1606,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1621,7 +1636,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1633,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1648,7 +1663,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1660,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1675,7 +1690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1687,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1702,7 +1717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1714,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1741,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1756,7 +1771,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1783,7 +1798,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1795,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1822,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1837,7 +1852,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1849,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1876,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1891,7 +1906,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1903,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1930,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1957,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1984,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2011,83 +2026,110 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>4339100.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>517875.7</t>
+          <t>4409100.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>514615</t>
+          <t>526517.68</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>514615</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>3260.7</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>11902.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1378,12 +1378,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1405,12 +1405,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1486,12 +1486,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1540,12 +1540,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1594,12 +1594,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1648,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1702,12 +1702,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1729,12 +1729,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1810,12 +1810,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1864,12 +1864,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1918,12 +1918,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1972,12 +1972,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1999,12 +1999,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2026,12 +2026,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2053,83 +2053,110 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>4409100.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>526517.68</t>
+          <t>4409100.1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>514615</t>
+          <t>526517.68</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>523256</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>11902.68</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3261.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,166 +1251,181 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1420,7 +1435,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1432,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1459,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1474,7 +1489,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1486,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1513,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1540,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1555,7 +1570,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1567,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1582,7 +1597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1594,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1621,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1648,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1675,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1690,7 +1705,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1702,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1717,7 +1732,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1729,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1756,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1771,7 +1786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1783,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1825,7 +1840,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1837,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1852,7 +1867,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1864,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1891,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1906,7 +1921,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1918,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1945,12 +1960,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1960,7 +1975,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1972,12 +1987,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1999,12 +2014,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2026,12 +2041,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2053,12 +2068,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2080,83 +2095,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>4409100.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>526517.68</t>
+          <t>4435098.1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>523256</t>
+          <t>529505.95</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>523256</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>3261.68</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6249.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1420,12 +1420,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1582,12 +1582,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1663,12 +1663,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1744,12 +1744,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1798,12 +1798,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1879,12 +1879,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1906,12 +1906,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1960,12 +1960,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2122,83 +2122,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>4435098.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>529505.95</t>
+          <t>4435098.1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>523256</t>
+          <t>529505.95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>526244</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>6249.95</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3261.95</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,166 +1293,181 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1474,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1489,7 +1504,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1501,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1528,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1543,7 +1558,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1555,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1582,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1609,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1624,7 +1639,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1636,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1651,7 +1666,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1663,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1690,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1717,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1744,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1759,7 +1774,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1771,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1786,7 +1801,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1798,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1813,7 +1828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1825,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1879,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1894,7 +1909,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1906,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1921,7 +1936,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1933,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1960,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1975,7 +1990,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1987,12 +2002,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2014,12 +2029,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2029,7 +2044,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2041,12 +2056,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2068,12 +2083,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2095,12 +2110,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2122,12 +2137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2149,83 +2164,110 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>4435098.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>529505.95</t>
+          <t>4715098.1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>526244</t>
+          <t>562839.28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>526244</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>3261.95</t>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>36595.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1462,12 +1462,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1543,12 +1543,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1597,12 +1597,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1624,12 +1624,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1651,12 +1651,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1678,12 +1678,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1705,12 +1705,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1732,12 +1732,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1786,12 +1786,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1813,12 +1813,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1894,12 +1894,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1921,12 +1921,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1948,12 +1948,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1975,12 +1975,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2002,12 +2002,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2056,12 +2056,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2110,12 +2110,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2137,12 +2137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2164,12 +2164,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2191,83 +2191,110 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>4715098.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>562839.28</t>
+          <t>4715098.1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>526244</t>
+          <t>562839.28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>559577</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>36595.28</t>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>3262.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,166 +1335,181 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1504,7 +1519,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1543,12 +1558,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1558,7 +1573,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1570,12 +1585,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1597,12 +1612,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1612,7 +1627,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1624,12 +1639,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1651,12 +1666,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1678,12 +1693,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1693,7 +1708,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1705,12 +1720,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1720,7 +1735,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1732,12 +1747,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1759,12 +1774,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1786,12 +1801,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1813,12 +1828,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1828,7 +1843,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1840,12 +1855,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1855,7 +1870,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1867,12 +1882,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1882,7 +1897,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1894,12 +1909,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1909,7 +1924,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1921,12 +1936,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1948,12 +1963,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1963,7 +1978,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1975,12 +1990,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1990,7 +2005,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2002,12 +2017,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2029,12 +2044,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2056,12 +2071,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2083,12 +2098,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2098,7 +2113,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2110,12 +2125,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2137,12 +2152,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2164,12 +2179,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2191,12 +2206,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2218,83 +2233,110 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>4715098.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>562839.28</t>
+          <t>4758394.1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>559577</t>
+          <t>567815.84</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>559577</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>3262.28</t>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>8238.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,166 +1377,181 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1546,7 +1561,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1585,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1600,7 +1615,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1612,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1639,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1654,7 +1669,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1666,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1693,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1720,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1735,7 +1750,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1747,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1762,7 +1777,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1774,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1801,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1828,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1855,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1870,7 +1885,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1882,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1897,7 +1912,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1909,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1924,7 +1939,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1936,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1963,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1990,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2005,7 +2020,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2017,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2044,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2071,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2086,7 +2101,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2098,12 +2113,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2125,12 +2140,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2140,7 +2155,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2152,12 +2167,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2179,12 +2194,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2206,12 +2221,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2233,12 +2248,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2260,83 +2275,110 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>4758394.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>567815.84</t>
+          <t>4870283.1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>559577</t>
+          <t>580676.64</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>559577</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>8238.84</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21099.64</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1546,12 +1546,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1573,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1600,12 +1600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1708,12 +1708,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1816,12 +1816,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1843,12 +1843,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1870,12 +1870,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1978,12 +1978,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2140,12 +2140,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2194,12 +2194,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2275,12 +2275,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2302,83 +2302,110 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>4870283.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>580676.64</t>
+          <t>4870283.1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>559577</t>
+          <t>580676.64</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>577414</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>21099.64</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3262.64</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,166 +1419,181 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1615,7 +1630,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1627,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1654,12 +1669,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1669,7 +1684,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1681,12 +1696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1708,12 +1723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1723,7 +1738,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1735,12 +1750,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1762,12 +1777,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1789,12 +1804,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1804,7 +1819,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1816,12 +1831,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1831,7 +1846,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1843,12 +1858,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1870,12 +1885,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1897,12 +1912,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1924,12 +1939,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1939,7 +1954,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1951,12 +1966,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1966,7 +1981,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1978,12 +1993,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1993,7 +2008,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2005,12 +2020,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2020,7 +2035,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2032,12 +2047,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2059,12 +2074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2074,7 +2089,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2086,12 +2101,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2113,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2140,12 +2155,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2155,7 +2170,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2167,12 +2182,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2194,12 +2209,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2209,7 +2224,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2221,12 +2236,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2248,12 +2263,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2275,12 +2290,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2302,12 +2317,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2329,83 +2344,110 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>4870283.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>580676.64</t>
+          <t>5180283.1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>577414</t>
+          <t>617802.39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>577414</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>3262.64</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>40388.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1588,12 +1588,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1642,12 +1642,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1669,12 +1669,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1750,12 +1750,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1777,12 +1777,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1804,12 +1804,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1858,12 +1858,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1885,12 +1885,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1939,12 +1939,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1966,12 +1966,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2020,12 +2020,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2074,12 +2074,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2101,12 +2101,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2128,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2182,12 +2182,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2236,12 +2236,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2317,12 +2317,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2344,12 +2344,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2371,83 +2371,110 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>5180283.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>617802.39</t>
+          <t>5180283.1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>577414</t>
+          <t>617802.39</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>614539</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>40388.39</t>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3263.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,166 +1461,181 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1630,7 +1645,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1669,12 +1684,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1684,7 +1699,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1696,12 +1711,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1723,12 +1738,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1738,7 +1753,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1750,12 +1765,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1777,12 +1792,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1792,7 +1807,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1804,12 +1819,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1831,12 +1846,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1858,12 +1873,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1873,7 +1888,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1885,12 +1900,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1900,7 +1915,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1912,12 +1927,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1939,12 +1954,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1966,12 +1981,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1993,12 +2008,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2008,7 +2023,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2020,12 +2035,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2035,7 +2050,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2047,12 +2062,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2062,7 +2077,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2074,12 +2089,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2089,7 +2104,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2101,12 +2116,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2128,12 +2143,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2143,7 +2158,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2155,12 +2170,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2170,7 +2185,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2182,12 +2197,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2209,12 +2224,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2224,7 +2239,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2236,12 +2251,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2263,12 +2278,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2278,7 +2293,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2290,12 +2305,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2317,12 +2332,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2344,12 +2359,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2371,12 +2386,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2398,83 +2413,110 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>5180283.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>617802.39</t>
+          <t>5188482.1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>614539</t>
+          <t>618744.8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>614539</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>3263.39</t>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4205.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,166 +1503,181 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1672,7 +1687,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1711,12 +1726,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1726,7 +1741,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1738,12 +1753,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1765,12 +1780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1780,7 +1795,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1792,12 +1807,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1819,12 +1834,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1834,7 +1849,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1846,12 +1861,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1873,12 +1888,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1900,12 +1915,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1915,7 +1930,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1927,12 +1942,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1942,7 +1957,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1954,12 +1969,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1981,12 +1996,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2008,12 +2023,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2035,12 +2050,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2050,7 +2065,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2062,12 +2077,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2077,7 +2092,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2089,12 +2104,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2104,7 +2119,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2116,12 +2131,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2131,7 +2146,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2143,12 +2158,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2170,12 +2185,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2185,7 +2200,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2197,12 +2212,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2212,7 +2227,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2224,12 +2239,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2251,12 +2266,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2266,7 +2281,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2278,12 +2293,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2305,12 +2320,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2320,7 +2335,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2332,12 +2347,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2359,12 +2374,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2386,12 +2401,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2413,12 +2428,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2440,83 +2455,110 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>5188482.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>618744.8</t>
+          <t>5338482.1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>614539</t>
+          <t>636391.86</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>614539</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>4205.8</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>21852.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1672,12 +1672,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1726,12 +1726,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1753,12 +1753,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1834,12 +1834,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1942,12 +1942,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1996,12 +1996,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2023,12 +2023,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2050,12 +2050,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2212,12 +2212,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2320,12 +2320,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2401,12 +2401,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2428,12 +2428,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2455,12 +2455,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2482,83 +2482,110 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>5338482.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>636391.86</t>
+          <t>5338482.1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>614539</t>
+          <t>636391.86</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>633128</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>21852.86</t>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>3263.86</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,166 +1545,181 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1714,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1741,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1753,12 +1768,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1780,12 +1795,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1795,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1807,12 +1822,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1834,12 +1849,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1849,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1861,12 +1876,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1888,12 +1903,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1903,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1915,12 +1930,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1942,12 +1957,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1969,12 +1984,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1984,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1996,12 +2011,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2011,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2023,12 +2038,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2050,12 +2065,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2077,12 +2092,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2104,12 +2119,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2119,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2131,12 +2146,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2146,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2158,12 +2173,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2173,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2185,12 +2200,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2200,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2212,12 +2227,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2239,12 +2254,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2254,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2266,12 +2281,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2281,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2293,12 +2308,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2320,12 +2335,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2335,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2347,12 +2362,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2374,12 +2389,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2389,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2401,12 +2416,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2428,12 +2443,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2455,12 +2470,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2482,12 +2497,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2509,83 +2524,110 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>5338482.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>636391.86</t>
+          <t>5403276.1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>633128</t>
+          <t>643839.45</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>633128</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>3263.86</t>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>10711.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1714,12 +1714,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1768,12 +1768,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1822,12 +1822,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1903,12 +1903,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1930,12 +1930,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1957,12 +1957,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2038,12 +2038,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2065,12 +2065,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2119,12 +2119,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2173,12 +2173,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2200,12 +2200,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2254,12 +2254,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2308,12 +2308,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2362,12 +2362,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2389,12 +2389,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2470,12 +2470,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2497,12 +2497,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2524,12 +2524,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2551,83 +2551,110 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>5403276.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>643839.45</t>
+          <t>5403276.1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>633128</t>
+          <t>643839.45</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>640575</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>10711.45</t>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>3264.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,166 +1587,181 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,7 +1771,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,7 +1798,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1795,12 +1810,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,7 +1825,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1822,12 +1837,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1849,12 +1864,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,7 +1879,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1876,12 +1891,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1903,12 +1918,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,7 +1933,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1930,12 +1945,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1957,12 +1972,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,7 +1987,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1984,12 +1999,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2011,12 +2026,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2038,12 +2053,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,7 +2068,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2065,12 +2080,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,7 +2095,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2092,12 +2107,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2119,12 +2134,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2146,12 +2161,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2173,12 +2188,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,7 +2203,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2200,12 +2215,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,7 +2230,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2227,12 +2242,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,7 +2257,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2254,12 +2269,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,7 +2284,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2281,12 +2296,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2308,12 +2323,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,7 +2338,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2335,12 +2350,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,7 +2365,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2362,12 +2377,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2389,12 +2404,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,7 +2419,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2416,12 +2431,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2443,12 +2458,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,7 +2473,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2470,12 +2485,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2497,12 +2512,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2524,12 +2539,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2551,12 +2566,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2578,83 +2593,110 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>5403276.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>643839.45</t>
+          <t>5430273.1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>640575</t>
+          <t>646942.55</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>640575</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>3264.45</t>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>6367.55</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,166 +1629,181 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1798,7 +1813,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1825,7 +1840,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1837,12 +1852,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1852,7 +1867,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1864,12 +1879,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1891,12 +1906,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1906,7 +1921,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1918,12 +1933,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1945,12 +1960,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1960,7 +1975,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1972,12 +1987,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1999,12 +2014,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2014,7 +2029,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2026,12 +2041,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2053,12 +2068,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2080,12 +2095,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2095,7 +2110,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2107,12 +2122,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2122,7 +2137,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2134,12 +2149,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2161,12 +2176,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2188,12 +2203,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2215,12 +2230,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2230,7 +2245,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2242,12 +2257,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2257,7 +2272,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2269,12 +2284,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2284,7 +2299,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2296,12 +2311,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2311,7 +2326,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2323,12 +2338,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2350,12 +2365,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2365,7 +2380,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2377,12 +2392,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2392,7 +2407,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2404,12 +2419,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2431,12 +2446,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2446,7 +2461,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2458,12 +2473,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2485,12 +2500,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2500,7 +2515,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2512,12 +2527,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2539,12 +2554,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2566,12 +2581,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2593,12 +2608,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2620,83 +2635,110 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>5430273.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>646942.55</t>
+          <t>5439472.1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>640575</t>
+          <t>647999.91</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>640575</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>6367.55</t>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7424.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1798,12 +1798,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1852,12 +1852,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1879,12 +1879,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1906,12 +1906,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1960,12 +1960,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1987,12 +1987,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2014,12 +2014,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2068,12 +2068,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2122,12 +2122,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2149,12 +2149,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2176,12 +2176,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2230,12 +2230,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2257,12 +2257,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2284,12 +2284,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2338,12 +2338,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2365,12 +2365,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2419,12 +2419,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2446,12 +2446,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2473,12 +2473,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2500,12 +2500,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2554,12 +2554,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2608,12 +2608,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2662,83 +2662,110 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>5439472.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>647999.91</t>
+          <t>5439472.1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>640575</t>
+          <t>647999.91</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>644735</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>7424.91</t>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3264.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,166 +1671,181 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1867,7 +1882,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1879,12 +1894,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1894,7 +1909,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1906,12 +1921,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1921,7 +1936,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1933,12 +1948,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1960,12 +1975,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1975,7 +1990,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1987,12 +2002,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2014,12 +2029,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2029,7 +2044,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2041,12 +2056,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2068,12 +2083,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2083,7 +2098,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2095,12 +2110,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2122,12 +2137,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2149,12 +2164,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2164,7 +2179,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2176,12 +2191,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2191,7 +2206,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2203,12 +2218,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2230,12 +2245,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2257,12 +2272,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2284,12 +2299,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2299,7 +2314,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2311,12 +2326,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2326,7 +2341,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2338,12 +2353,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2353,7 +2368,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2365,12 +2380,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2380,7 +2395,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2392,12 +2407,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2419,12 +2434,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2434,7 +2449,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2446,12 +2461,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2461,7 +2476,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2473,12 +2488,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2500,12 +2515,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2515,7 +2530,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2527,12 +2542,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2554,12 +2569,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2569,7 +2584,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2581,12 +2596,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2608,12 +2623,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2635,12 +2650,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2662,12 +2677,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2689,83 +2704,110 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>5439472.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>647999.91</t>
+          <t>5939472.1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>644735</t>
+          <t>708240.87</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>644735</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3264.91</t>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>63505.87</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,166 +1713,181 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1894,12 +1909,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1909,7 +1924,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1921,12 +1936,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1936,7 +1951,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1948,12 +1963,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1963,7 +1978,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1975,12 +1990,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2002,12 +2017,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2017,7 +2032,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2029,12 +2044,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2056,12 +2071,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2071,7 +2086,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2083,12 +2098,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2110,12 +2125,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2125,7 +2140,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2137,12 +2152,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2164,12 +2179,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2191,12 +2206,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2206,7 +2221,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2218,12 +2233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2233,7 +2248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2245,12 +2260,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2272,12 +2287,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2299,12 +2314,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2326,12 +2341,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2341,7 +2356,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2353,12 +2368,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2368,7 +2383,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2380,12 +2395,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2395,7 +2410,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2407,12 +2422,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2422,7 +2437,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2434,12 +2449,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2461,12 +2476,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2488,12 +2503,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2503,7 +2518,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2515,12 +2530,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2542,12 +2557,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2557,7 +2572,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2569,12 +2584,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2596,12 +2611,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2611,7 +2626,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2623,12 +2638,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2650,12 +2665,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2677,12 +2692,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2704,12 +2719,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2731,83 +2746,110 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>5939472.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>708240.87</t>
+          <t>6109472.1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>644735</t>
+          <t>728478.97</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>644735</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>63505.87</t>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>83743.97</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1882,12 +1882,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1936,12 +1936,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1990,12 +1990,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2017,12 +2017,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2071,12 +2071,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2098,12 +2098,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2125,12 +2125,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2179,12 +2179,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2206,12 +2206,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2233,12 +2233,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2260,12 +2260,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2314,12 +2314,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2395,12 +2395,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2422,12 +2422,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2449,12 +2449,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2503,12 +2503,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2584,12 +2584,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2611,12 +2611,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2665,12 +2665,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2719,12 +2719,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2746,12 +2746,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2773,83 +2773,110 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>6109472.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>728478.97</t>
+          <t>6109472.1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>644735</t>
+          <t>728478.97</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>725214</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>83743.97</t>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3264.97</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,166 +1755,181 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1936,12 +1951,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1963,12 +1978,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1978,7 +1993,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1990,12 +2005,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2005,7 +2020,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2017,12 +2032,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2032,7 +2047,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2044,12 +2059,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2071,12 +2086,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2086,7 +2101,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2098,12 +2113,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2125,12 +2140,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2140,7 +2155,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2152,12 +2167,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2179,12 +2194,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2194,7 +2209,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2206,12 +2221,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2233,12 +2248,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2260,12 +2275,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2275,7 +2290,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2287,12 +2302,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2302,7 +2317,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2314,12 +2329,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2341,12 +2356,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2368,12 +2383,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2395,12 +2410,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2410,7 +2425,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2422,12 +2437,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2437,7 +2452,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2449,12 +2464,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2464,7 +2479,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2476,12 +2491,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2491,7 +2506,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2503,12 +2518,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2530,12 +2545,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2545,7 +2560,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2557,12 +2572,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2572,7 +2587,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2584,12 +2599,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2611,12 +2626,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2626,7 +2641,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2638,12 +2653,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2665,12 +2680,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2680,7 +2695,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2692,12 +2707,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2719,12 +2734,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2746,12 +2761,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2773,12 +2788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2800,83 +2815,110 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>6109472.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>728478.97</t>
+          <t>6142469.1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>725214</t>
+          <t>732271.73</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>725214</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>3264.97</t>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7057.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1924,12 +1924,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1978,12 +1978,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2140,12 +2140,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2194,12 +2194,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2221,12 +2221,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2275,12 +2275,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2302,12 +2302,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2329,12 +2329,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2356,12 +2356,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2410,12 +2410,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2437,12 +2437,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2518,12 +2518,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2572,12 +2572,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2626,12 +2626,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2653,12 +2653,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2734,12 +2734,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2815,12 +2815,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2842,83 +2842,110 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>6142469.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>732271.73</t>
+          <t>6142469.1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>725214</t>
+          <t>732271.73</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>729006</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7057.73</t>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3265.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,166 +1797,181 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1978,12 +1993,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2005,12 +2020,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2032,12 +2047,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2047,7 +2062,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2059,12 +2074,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2074,7 +2089,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2086,12 +2101,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2101,7 +2116,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2113,12 +2128,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2140,12 +2155,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2155,7 +2170,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2167,12 +2182,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2194,12 +2209,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2209,7 +2224,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2221,12 +2236,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2248,12 +2263,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2263,7 +2278,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2275,12 +2290,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2302,12 +2317,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2329,12 +2344,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2344,7 +2359,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2356,12 +2371,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2371,7 +2386,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2383,12 +2398,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2410,12 +2425,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2437,12 +2452,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2464,12 +2479,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2479,7 +2494,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2491,12 +2506,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2506,7 +2521,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2518,12 +2533,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2533,7 +2548,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2545,12 +2560,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2560,7 +2575,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2572,12 +2587,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2599,12 +2614,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2614,7 +2629,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2626,12 +2641,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2641,7 +2656,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2653,12 +2668,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2680,12 +2695,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2695,7 +2710,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2707,12 +2722,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2734,12 +2749,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2749,7 +2764,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2761,12 +2776,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2788,12 +2803,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2815,12 +2830,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2842,12 +2857,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2869,83 +2884,110 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>6142469.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>732271.73</t>
+          <t>6151668.1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>729006</t>
+          <t>733329.08</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>729006</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3265.73</t>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>4323.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -1966,12 +1966,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2020,12 +2020,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2047,12 +2047,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2074,12 +2074,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2101,12 +2101,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2128,12 +2128,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2182,12 +2182,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2236,12 +2236,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2263,12 +2263,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2317,12 +2317,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2344,12 +2344,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2398,12 +2398,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2479,12 +2479,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2506,12 +2506,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2533,12 +2533,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2560,12 +2560,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2587,12 +2587,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2614,12 +2614,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2695,12 +2695,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2722,12 +2722,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2776,12 +2776,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2803,12 +2803,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2857,12 +2857,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2911,83 +2911,110 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>6151668.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>733329.08</t>
+          <t>6151668.1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>729006</t>
+          <t>733329.08</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>730063</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>4323.08</t>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3266.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,166 +1839,181 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2020,12 +2035,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2047,12 +2062,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2074,12 +2089,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2101,12 +2116,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2116,7 +2131,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2128,12 +2143,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2143,7 +2158,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2155,12 +2170,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2170,7 +2185,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2182,12 +2197,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2209,12 +2224,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2224,7 +2239,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2236,12 +2251,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2263,12 +2278,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2278,7 +2293,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2290,12 +2305,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2317,12 +2332,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2332,7 +2347,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2344,12 +2359,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2371,12 +2386,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2398,12 +2413,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2413,7 +2428,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2425,12 +2440,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2440,7 +2455,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2452,12 +2467,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2479,12 +2494,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2506,12 +2521,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2533,12 +2548,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2548,7 +2563,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2560,12 +2575,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2575,7 +2590,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2587,12 +2602,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2602,7 +2617,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2614,12 +2629,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2629,7 +2644,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2641,12 +2656,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2668,12 +2683,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2683,7 +2698,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2695,12 +2710,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2710,7 +2725,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2722,12 +2737,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2749,12 +2764,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2764,7 +2779,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2776,12 +2791,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2803,12 +2818,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2818,7 +2833,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2830,12 +2845,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2857,12 +2872,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2884,12 +2899,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2911,12 +2926,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2938,83 +2953,110 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>6151668.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>733329.08</t>
+          <t>6451668.1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>730063</t>
+          <t>768623.2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>730063</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>3266.08</t>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>38560.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,166 +1881,181 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2050,7 +2065,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2062,12 +2077,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2089,12 +2104,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2116,12 +2131,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2143,12 +2158,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2158,7 +2173,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2170,12 +2185,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2197,12 +2212,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2224,12 +2239,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2239,7 +2254,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2251,12 +2266,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2266,7 +2281,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2278,12 +2293,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2293,7 +2308,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2305,12 +2320,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2320,7 +2335,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2332,12 +2347,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2347,7 +2362,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2359,12 +2374,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2374,7 +2389,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2386,12 +2401,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2401,7 +2416,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2413,12 +2428,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2440,12 +2455,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2455,7 +2470,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2467,12 +2482,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2494,12 +2509,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2509,7 +2524,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2521,12 +2536,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2548,12 +2563,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2575,12 +2590,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2590,7 +2605,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2602,12 +2617,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2629,12 +2644,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2656,12 +2671,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2683,12 +2698,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2698,7 +2713,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2710,12 +2725,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2725,7 +2740,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2737,12 +2752,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2764,12 +2779,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2779,7 +2794,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2791,12 +2806,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2806,7 +2821,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2818,12 +2833,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2833,7 +2848,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2845,12 +2860,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2860,7 +2875,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2872,12 +2887,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2887,7 +2902,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2899,12 +2914,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2926,12 +2941,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2953,12 +2968,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2980,12 +2995,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/26 14:18:46</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3004,59 +3019,113 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>6451668.1</t>
-        </is>
-      </c>
-    </row>
+          <t>06/26 14:18:46</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>768623.2</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>730063</t>
+          <t>7251668.1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>859532.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>730651</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>38560.2</t>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>128881.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2050,12 +2050,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2104,12 +2104,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2158,12 +2158,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2212,12 +2212,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2266,12 +2266,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2320,12 +2320,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2401,12 +2401,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2428,12 +2428,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2455,12 +2455,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2536,12 +2536,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2563,12 +2563,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2590,12 +2590,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2617,12 +2617,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2644,12 +2644,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2698,12 +2698,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2725,12 +2725,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2779,12 +2779,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2806,12 +2806,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2860,12 +2860,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2914,12 +2914,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2941,12 +2941,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2995,12 +2995,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3022,12 +3022,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3049,83 +3049,110 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="94"/>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>7251668.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>859532.29</t>
+          <t>7251668.1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>730651</t>
+          <t>859532.29</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>856266</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>128881.29</t>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>3266.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,166 +1923,181 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2104,12 +2119,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2119,7 +2134,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2131,12 +2146,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2158,12 +2173,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2185,12 +2200,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2212,12 +2227,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2239,12 +2254,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2254,7 +2269,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2266,12 +2281,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2281,7 +2296,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2293,12 +2308,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2308,7 +2323,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2320,12 +2335,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2347,12 +2362,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2362,7 +2377,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2374,12 +2389,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2401,12 +2416,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2416,7 +2431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2428,12 +2443,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2455,12 +2470,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2470,7 +2485,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2482,12 +2497,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2509,12 +2524,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2536,12 +2551,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2551,7 +2566,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2563,12 +2578,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2578,7 +2593,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2590,12 +2605,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2617,12 +2632,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2644,12 +2659,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2671,12 +2686,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2686,7 +2701,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2698,12 +2713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2713,7 +2728,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2725,12 +2740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2740,7 +2755,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2752,12 +2767,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2767,7 +2782,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2779,12 +2794,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2806,12 +2821,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2821,7 +2836,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2833,12 +2848,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2848,7 +2863,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2860,12 +2875,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2887,12 +2902,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2902,7 +2917,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2914,12 +2929,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2941,12 +2956,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2956,7 +2971,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2968,12 +2983,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2995,12 +3010,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3022,12 +3037,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3049,12 +3064,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3076,83 +3091,110 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>7251668.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>859532.29</t>
+          <t>7264667.1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>856266</t>
+          <t>861026.43</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>856266</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>3266.29</t>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4760.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 11:41:36</t>
+          <t>10/08 11:42:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>5061.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>410000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>50617.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/26 08:48:20</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2004,154 +2004,184 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06/26 08:48:20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>36144.58</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>代付</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>费率</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>汇率</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>结算</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>费率</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>汇率</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>结算</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>125615</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2161,7 +2191,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2173,12 +2203,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2188,7 +2218,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2200,12 +2230,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2227,12 +2257,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2254,12 +2284,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2281,12 +2311,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2296,7 +2326,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2308,12 +2338,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2335,12 +2365,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2362,12 +2392,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2377,7 +2407,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2389,12 +2419,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2404,7 +2434,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2416,12 +2446,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2431,7 +2461,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2443,12 +2473,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2458,7 +2488,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2470,12 +2500,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2485,7 +2515,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2497,12 +2527,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2512,7 +2542,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2524,12 +2554,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2539,7 +2569,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2551,12 +2581,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2578,12 +2608,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2605,12 +2635,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2632,12 +2662,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2647,7 +2677,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2659,12 +2689,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2686,12 +2716,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2713,12 +2743,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2728,7 +2758,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2740,12 +2770,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2767,12 +2797,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2794,12 +2824,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2821,12 +2851,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2836,7 +2866,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2848,12 +2878,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2863,7 +2893,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2875,12 +2905,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2902,12 +2932,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2917,7 +2947,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2929,12 +2959,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2944,7 +2974,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2956,12 +2986,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2971,7 +3001,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2983,12 +3013,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2998,7 +3028,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3010,12 +3040,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3025,7 +3055,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3037,12 +3067,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3064,12 +3094,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3091,12 +3121,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3118,12 +3148,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/26 14:18:46</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>55192</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3142,59 +3172,113 @@
         </is>
       </c>
     </row>
-    <row r="96"/>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>7264667.1</t>
-        </is>
-      </c>
-    </row>
+          <t>06/26 14:18:46</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>55192</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>861026.43</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>856266</t>
+          <t>7715667.1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>916705.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>856266</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>4760.43</t>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>60439.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2176,12 +2176,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2203,12 +2203,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2230,12 +2230,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2257,12 +2257,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2284,12 +2284,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2338,12 +2338,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2365,12 +2365,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2419,12 +2419,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2446,12 +2446,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2473,12 +2473,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2500,12 +2500,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2527,12 +2527,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2554,12 +2554,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2608,12 +2608,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2662,12 +2662,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2716,12 +2716,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2743,12 +2743,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2824,12 +2824,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2851,12 +2851,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2878,12 +2878,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2905,12 +2905,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2932,12 +2932,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2986,12 +2986,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3013,12 +3013,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3040,12 +3040,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3067,12 +3067,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3094,12 +3094,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3121,12 +3121,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3148,12 +3148,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3175,12 +3175,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3202,83 +3202,110 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>7715667.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>916705.44</t>
+          <t>7715667.1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>856266</t>
+          <t>916705.44</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>862821</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>60439.44</t>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>53884.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 11:42:30</t>
+          <t>10/09 11:17:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5061.73</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 11:41:49</t>
+          <t>10/08 11:42:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50617.28</t>
+          <t>5061.73</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 11:41:36</t>
+          <t>10/08 11:41:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>410000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>50617.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,166 +2049,181 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2218,7 +2233,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2230,12 +2245,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2257,12 +2272,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2272,7 +2287,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2284,12 +2299,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2311,12 +2326,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2338,12 +2353,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2365,12 +2380,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2392,12 +2407,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2407,7 +2422,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2419,12 +2434,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2434,7 +2449,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2446,12 +2461,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2461,7 +2476,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2473,12 +2488,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2500,12 +2515,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2515,7 +2530,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2527,12 +2542,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2554,12 +2569,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2569,7 +2584,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2581,12 +2596,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2608,12 +2623,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2623,7 +2638,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2635,12 +2650,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2662,12 +2677,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2689,12 +2704,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2704,7 +2719,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2716,12 +2731,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2731,7 +2746,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2743,12 +2758,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2770,12 +2785,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2797,12 +2812,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2824,12 +2839,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2839,7 +2854,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2851,12 +2866,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2866,7 +2881,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2878,12 +2893,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2893,7 +2908,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2905,12 +2920,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2920,7 +2935,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2932,12 +2947,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2959,12 +2974,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2974,7 +2989,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2986,12 +3001,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3001,7 +3016,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3013,12 +3028,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3040,12 +3055,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3055,7 +3070,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3067,12 +3082,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3094,12 +3109,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3109,7 +3124,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3121,12 +3136,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3148,12 +3163,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3175,12 +3190,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3202,12 +3217,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3229,83 +3244,110 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>7715667.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>916705.44</t>
+          <t>7815667.1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>862821</t>
+          <t>928470.15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>862821</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>53884.44</t>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>65649.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2218,12 +2218,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2272,12 +2272,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2326,12 +2326,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2353,12 +2353,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2380,12 +2380,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2434,12 +2434,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2488,12 +2488,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2515,12 +2515,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2542,12 +2542,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2569,12 +2569,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2596,12 +2596,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2650,12 +2650,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2677,12 +2677,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2704,12 +2704,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2758,12 +2758,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2785,12 +2785,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2812,12 +2812,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2839,12 +2839,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2866,12 +2866,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2893,12 +2893,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2920,12 +2920,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2947,12 +2947,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2974,12 +2974,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3001,12 +3001,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3028,12 +3028,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3055,12 +3055,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3082,12 +3082,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3136,12 +3136,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3163,12 +3163,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3190,12 +3190,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3244,12 +3244,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3271,83 +3271,110 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>7815667.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>928470.15</t>
+          <t>7815667.1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>862821</t>
+          <t>928470.15</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>874585</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>65649.15</t>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>53885.15</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 11:17:22</t>
+          <t>10/10 10:51:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>1264.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 11:42:30</t>
+          <t>10/09 11:17:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5061.73</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 11:41:49</t>
+          <t>10/08 11:42:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50617.28</t>
+          <t>5061.73</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 11:41:36</t>
+          <t>10/08 11:41:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>410000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>50617.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,166 +2091,181 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2260,7 +2275,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2272,12 +2287,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2287,7 +2302,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2299,12 +2314,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2326,12 +2341,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2341,7 +2356,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2353,12 +2368,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2380,12 +2395,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2407,12 +2422,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2434,12 +2449,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2461,12 +2476,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2488,12 +2503,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2503,7 +2518,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2515,12 +2530,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2530,7 +2545,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2542,12 +2557,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2569,12 +2584,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2584,7 +2599,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2596,12 +2611,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2623,12 +2638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2638,7 +2653,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2650,12 +2665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2677,12 +2692,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2692,7 +2707,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2704,12 +2719,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2731,12 +2746,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2758,12 +2773,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2773,7 +2788,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2785,12 +2800,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2800,7 +2815,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2812,12 +2827,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2839,12 +2854,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2866,12 +2881,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2893,12 +2908,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2908,7 +2923,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2920,12 +2935,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2935,7 +2950,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2947,12 +2962,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2962,7 +2977,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2974,12 +2989,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2989,7 +3004,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3001,12 +3016,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3028,12 +3043,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3043,7 +3058,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3055,12 +3070,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3070,7 +3085,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3082,12 +3097,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3109,12 +3124,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3124,7 +3139,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3136,12 +3151,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3163,12 +3178,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3178,7 +3193,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3190,12 +3205,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3217,12 +3232,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3244,12 +3259,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3271,12 +3286,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3298,83 +3313,110 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>7815667.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>928470.15</t>
+          <t>7826666.1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>874585</t>
+          <t>929734.4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>874585</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>53885.15</t>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>55149.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2260,12 +2260,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2314,12 +2314,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2368,12 +2368,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2395,12 +2395,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2422,12 +2422,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2449,12 +2449,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2476,12 +2476,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2503,12 +2503,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2584,12 +2584,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2611,12 +2611,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2638,12 +2638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2665,12 +2665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2719,12 +2719,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2746,12 +2746,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2773,12 +2773,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2800,12 +2800,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2908,12 +2908,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2935,12 +2935,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2989,12 +2989,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3070,12 +3070,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3097,12 +3097,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3124,12 +3124,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3178,12 +3178,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3205,12 +3205,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3232,12 +3232,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3286,12 +3286,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3313,12 +3313,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3340,83 +3340,110 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>7826666.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>929734.4</t>
+          <t>7826666.1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>874585</t>
+          <t>929734.4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>875849</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>55149.4</t>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>53885.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/10 10:51:19</t>
+          <t>10/15 11:34:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1264.25</t>
+          <t>35502.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09 11:17:22</t>
+          <t>10/10 10:51:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>1264.25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 11:42:30</t>
+          <t>10/09 11:17:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5061.73</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 11:41:49</t>
+          <t>10/08 11:42:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50617.28</t>
+          <t>5061.73</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08 11:41:36</t>
+          <t>10/08 11:41:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>410000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>50617.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,166 +2133,181 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10/11 14:24:40</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2314,12 +2329,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2329,7 +2344,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2341,12 +2356,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2356,7 +2371,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2368,12 +2383,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2395,12 +2410,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2410,7 +2425,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2422,12 +2437,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2449,12 +2464,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2476,12 +2491,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2503,12 +2518,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2530,12 +2545,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2545,7 +2560,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2557,12 +2572,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2572,7 +2587,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2584,12 +2599,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2599,7 +2614,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2611,12 +2626,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2638,12 +2653,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2653,7 +2668,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2665,12 +2680,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2692,12 +2707,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2707,7 +2722,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2719,12 +2734,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2746,12 +2761,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2761,7 +2776,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2773,12 +2788,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2800,12 +2815,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2827,12 +2842,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2842,7 +2857,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2854,12 +2869,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2869,7 +2884,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2881,12 +2896,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2908,12 +2923,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2935,12 +2950,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2962,12 +2977,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2977,7 +2992,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2989,12 +3004,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3004,7 +3019,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3016,12 +3031,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3031,7 +3046,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3043,12 +3058,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3058,7 +3073,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3070,12 +3085,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3097,12 +3112,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3112,7 +3127,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3124,12 +3139,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3139,7 +3154,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3151,12 +3166,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3178,12 +3193,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3193,7 +3208,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3205,12 +3220,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3232,12 +3247,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3247,7 +3262,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3259,12 +3274,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3286,12 +3301,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3313,12 +3328,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3340,12 +3355,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3367,83 +3382,110 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>7826666.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>929734.4</t>
+          <t>8126666.1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>875849</t>
+          <t>965237.36</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>875849</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>53885.4</t>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>89388.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2302,12 +2302,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/11 14:24:40</t>
+          <t>10/15 14:19:13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2329,12 +2329,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2356,12 +2356,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2410,12 +2410,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2437,12 +2437,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2464,12 +2464,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2518,12 +2518,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2572,12 +2572,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2599,12 +2599,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2626,12 +2626,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2653,12 +2653,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2734,12 +2734,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2815,12 +2815,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2842,12 +2842,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2869,12 +2869,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2896,12 +2896,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2950,12 +2950,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2977,12 +2977,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3004,12 +3004,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3058,12 +3058,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3112,12 +3112,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3139,12 +3139,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3193,12 +3193,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3220,12 +3220,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3274,12 +3274,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3301,12 +3301,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3355,12 +3355,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3382,12 +3382,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3409,83 +3409,110 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>8126666.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>965237.36</t>
+          <t>8126666.1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>875849</t>
+          <t>965237.36</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>911351</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>89388.36</t>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>53886.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/15 11:34:44</t>
+          <t>10/17 10:38:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35502.96</t>
+          <t>5470.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/10 10:51:19</t>
+          <t>10/15 11:34:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1264.25</t>
+          <t>35502.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09 11:17:22</t>
+          <t>10/10 10:51:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>1264.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 11:42:30</t>
+          <t>10/09 11:17:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5061.73</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08 11:41:49</t>
+          <t>10/08 11:42:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50617.28</t>
+          <t>5061.73</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/08 11:41:36</t>
+          <t>10/08 11:41:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>410000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1494.14</t>
+          <t>50617.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/07 15:29:43</t>
+          <t>10/08 11:41:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>90909.09</t>
+          <t>1494.14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/07 12:40:00</t>
+          <t>10/07 15:29:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35294.12</t>
+          <t>90909.09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 11:08:47</t>
+          <t>10/07 12:40:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>35294.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/02 09:47:32</t>
+          <t>10/06 11:08:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3792.76</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/01 12:25:33</t>
+          <t>10/02 09:47:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20238.1</t>
+          <t>3792.76</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/01 10:48:59</t>
+          <t>10/01 12:25:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>20238.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/28 12:36:34</t>
+          <t>10/01 10:48:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1057.36</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/28 12:35:24</t>
+          <t>09/28 12:36:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3103.1</t>
+          <t>1057.36</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/26 11:39:37</t>
+          <t>09/28 12:35:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7447.59</t>
+          <t>3103.1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 12:29:19</t>
+          <t>09/26 11:39:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17647.06</t>
+          <t>7447.59</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 11:26:49</t>
+          <t>09/25 12:29:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>942.41</t>
+          <t>17647.06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24 18:06:56</t>
+          <t>09/25 11:26:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37125.75</t>
+          <t>942.41</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 18:15:32</t>
+          <t>09/24 18:06:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12860.8</t>
+          <t>37125.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 10:57:59</t>
+          <t>09/23 18:15:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>111889</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4976.55</t>
+          <t>12860.8</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21 11:44:11</t>
+          <t>09/23 10:57:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33333.33</t>
+          <t>4976.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 09:38:01</t>
+          <t>09/21 11:44:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2988.28</t>
+          <t>33333.33</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/19 11:35:34</t>
+          <t>09/20 09:38:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8641.98</t>
+          <t>2988.28</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18 13:46:58</t>
+          <t>09/19 11:35:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>952.29</t>
+          <t>8641.98</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17 11:43:48</t>
+          <t>09/18 13:46:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1171.95</t>
+          <t>952.29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/15 12:39:48</t>
+          <t>09/17 11:43:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>1171.95</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/13 19:18:25</t>
+          <t>09/15 12:39:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3658.54</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/03 16:08:30</t>
+          <t>09/13 19:18:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>905.45</t>
+          <t>3658.54</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/03 10:40:31</t>
+          <t>09/03 16:08:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>905.45</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/28 15:05:35</t>
+          <t>09/03 10:40:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23529.41</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/05 15:01:21</t>
+          <t>08/28 15:05:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>23529.41</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/03 12:30:57</t>
+          <t>08/05 15:01:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>83443.5</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10176.04</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/02 13:25:14</t>
+          <t>08/03 12:30:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>83443.5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4938.27</t>
+          <t>10176.04</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/31 12:30:54</t>
+          <t>08/02 13:25:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7407.41</t>
+          <t>4938.27</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/25 19:32:44</t>
+          <t>07/31 12:30:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3689.31</t>
+          <t>7407.41</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/25 13:04:40</t>
+          <t>07/25 19:32:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>3689.31</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/25 11:57:40</t>
+          <t>07/25 13:04:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2344.6</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24 20:35:52</t>
+          <t>07/25 11:57:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5976.55</t>
+          <t>2344.6</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/22 16:06:43</t>
+          <t>07/24 20:35:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3758.28</t>
+          <t>5976.55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/22 11:02:56</t>
+          <t>07/22 16:06:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>3758.28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/21 14:23:03</t>
+          <t>07/22 11:02:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11976.05</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17 18:39:08</t>
+          <t>07/21 14:23:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>44578.31</t>
+          <t>11976.05</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17 10:47:05</t>
+          <t>07/17 18:39:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13443.22</t>
+          <t>44578.31</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/15 12:35:40</t>
+          <t>07/17 10:47:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29940.12</t>
+          <t>13443.22</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/10 13:25:31</t>
+          <t>07/15 12:35:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>29048.04</t>
+          <t>29940.12</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/09 14:23:27</t>
+          <t>07/10 13:25:31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>29048.04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/08 11:56:26</t>
+          <t>07/09 14:23:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>119047.62</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/07 17:03:46</t>
+          <t>07/08 11:56:26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>119047.62</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02 09:59:06</t>
+          <t>07/07 17:03:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26 10:01:15</t>
+          <t>07/02 09:59:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19047.62</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,166 +2175,181 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06/26 10:01:15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19047.62</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>06/26 08:48:20</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>300000</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>36144.58</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10/15 14:19:13</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/11 14:24:40</t>
+          <t>10/15 14:19:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2344,7 +2359,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2356,12 +2371,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2383,12 +2398,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2398,7 +2413,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2410,12 +2425,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2425,7 +2440,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2437,12 +2452,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2464,12 +2479,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2479,7 +2494,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2491,12 +2506,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2518,12 +2533,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2545,12 +2560,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2572,12 +2587,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2599,12 +2614,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2614,7 +2629,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2626,12 +2641,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2641,7 +2656,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2653,12 +2668,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2668,7 +2683,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2680,12 +2695,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2707,12 +2722,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2722,7 +2737,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2734,12 +2749,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2761,12 +2776,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2776,7 +2791,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2788,12 +2803,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2815,12 +2830,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2830,7 +2845,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2842,12 +2857,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2869,12 +2884,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2896,12 +2911,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2911,7 +2926,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2923,12 +2938,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2938,7 +2953,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2950,12 +2965,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2977,12 +2992,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3004,12 +3019,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3031,12 +3046,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3046,7 +3061,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3058,12 +3073,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3073,7 +3088,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3085,12 +3100,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3100,7 +3115,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3112,12 +3127,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3127,7 +3142,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3139,12 +3154,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3166,12 +3181,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3181,7 +3196,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3193,12 +3208,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3208,7 +3223,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3220,12 +3235,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3247,12 +3262,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3262,7 +3277,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3274,12 +3289,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3301,12 +3316,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3316,7 +3331,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3328,12 +3343,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3355,12 +3370,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3382,12 +3397,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3409,12 +3424,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3436,83 +3451,110 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="105"/>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>8126666.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>965237.36</t>
+          <t>8174263.1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>911351</t>
+          <t>970708.28</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>911351</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>53886.36</t>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>59357.28</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
+++ b/bills/JXZFSP01/-5290785690/812e70286f81cef582352dfd129c0c6d6f5b09ab14e4edd43b363fcc2595e1ca/bill-all.xlsx
@@ -2344,12 +2344,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10/15 14:19:13</t>
+          <t>10/17 18:42:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10/11 14:24:40</t>
+          <t>10/15 14:19:13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2398,12 +2398,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10/09 14:19:05</t>
+          <t>10/11 14:24:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10/08 16:54:46</t>
+          <t>10/09 14:19:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>jxzf0001</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10/07 18:45:49</t>
+          <t>10/08 16:54:46</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxzf0001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2479,12 +2479,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10/07 15:29:48</t>
+          <t>10/07 18:45:49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2506,12 +2506,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10/06 21:12:37</t>
+          <t>10/07 15:29:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>588</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2533,12 +2533,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10/02 19:08:01</t>
+          <t>10/06 21:12:37</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2560,12 +2560,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10/01 14:50:01</t>
+          <t>10/02 19:08:01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2587,12 +2587,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09/28 19:50:50</t>
+          <t>10/01 14:50:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2614,12 +2614,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09/26 14:24:59</t>
+          <t>09/28 19:50:50</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09/25 14:55:19</t>
+          <t>09/26 14:24:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09/24 19:45:39</t>
+          <t>09/25 14:55:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2695,12 +2695,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09/23 18:40:15</t>
+          <t>09/24 19:45:39</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2722,12 +2722,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09/21 13:13:00</t>
+          <t>09/23 18:40:15</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09/20 13:51:56</t>
+          <t>09/21 13:13:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2776,12 +2776,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09/19 16:32:00</t>
+          <t>09/20 13:51:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2803,12 +2803,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09/18 19:11:40</t>
+          <t>09/19 16:32:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09/17 17:19:54</t>
+          <t>09/18 19:11:40</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2857,12 +2857,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09/15 13:43:01</t>
+          <t>09/17 17:19:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2884,12 +2884,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09/13 19:21:10</t>
+          <t>09/15 13:43:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09/03 13:42:01</t>
+          <t>09/13 19:21:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2938,12 +2938,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08/28 17:06:04</t>
+          <t>09/03 13:42:01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2965,12 +2965,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08/28 15:10:12</t>
+          <t>08/28 17:06:04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2992,12 +2992,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08/05 16:20:51</t>
+          <t>08/28 15:10:12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>888</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08/03 14:06:46</t>
+          <t>08/05 16:20:51</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3046,12 +3046,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>08/02 14:59:07</t>
+          <t>08/03 14:06:46</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>07/31 16:20:29</t>
+          <t>08/02 14:59:07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3100,12 +3100,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>07/25 19:35:26</t>
+          <t>07/31 16:20:29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3127,12 +3127,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/24 20:41:55</t>
+          <t>07/25 19:35:26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3154,12 +3154,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/22 16:12:46</t>
+          <t>07/24 20:41:55</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3181,12 +3181,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/22 14:20:08</t>
+          <t>07/22 16:12:46</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3208,12 +3208,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/21 16:48:48</t>
+          <t>07/22 14:20:08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>26190</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07/17 19:46:52</t>
+          <t>07/21 16:48:48</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>56933</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3262,12 +3262,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07/17 18:39:32</t>
+          <t>07/17 19:46:52</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>56933</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3289,12 +3289,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07/17 10:47:27</t>
+          <t>07/17 18:39:32</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3316,12 +3316,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07/15 14:23:24</t>
+          <t>07/17 10:47:27</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3343,12 +3343,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07/10 18:09:01</t>
+          <t>07/15 14:23:24</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3370,12 +3370,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>07/09 16:13:47</t>
+          <t>07/10 18:09:01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3397,12 +3397,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>07/08 14:16:26</t>
+          <t>07/09 16:13:47</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>119047</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3424,12 +3424,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>07/07 18:23:19</t>
+          <t>07/08 14:16:26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3451,12 +3451,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>07/02 12:31:26</t>
+          <t>07/07 18:23:19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3478,83 +3478,110 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>07/02 12:31:26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>06/26 14:18:46</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>55192</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>8174263.1</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>970708.28</t>
+          <t>8174263.1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>911351</t>
+          <t>970708.28</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>916821</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>59357.28</t>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>53887.28</t>
         </is>
       </c>
     </row>
